--- a/_Learn/Packaging.tutorial/OS.11/25H2/Expand/Install/Report.Overview.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/25H2/Expand/Install/Report.Overview.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YiSolutions\_Learn\Packaging.tutorial\OS.11\25H2\Expand\Install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81962AF7-0824-484D-A863-F6B406FC3F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA814A47-424E-4384-A420-0491A8DA9EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report.Overview" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="116">
   <si>
     <t>Verify if it is published by Yi</t>
   </si>
@@ -326,6 +326,265 @@
   </si>
   <si>
     <t>zh-HK</t>
+  </si>
+  <si>
+    <t>Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-Basic-fr-fr-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-Handwriting-fr-fr-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+</t>
+  </si>
+  <si>
+    <t>Microsoft-Windows-LanguageFeatures-Basic-zh-hk-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-Speech-zh-hk-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-TextToSpeech-zh-hk-Package~31bf3856ad364e35~amd64~~10.0.26100.1742</t>
+  </si>
+  <si>
+    <t>Report: Windows 11 25H2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+zh-tw_windows_11_consumer_editions_version_25h2_x64_dvd_5c984625.iso
+zh-tw_windows_11_business_editions_version_25h2_x64_dvd_fc876202.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+zh-cn_windows_11_consumer_editions_version_25h2_x64_dvd_0549fc93.iso
+zh-cn_windows_11_business_editions_version_25h2_x64_dvd_22759158.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+uk-ua_windows_11_consumer_editions_version_25h2_x64_dvd_422284c8.iso
+uk-ua_windows_11_business_editions_version_25h2_x64_dvd_2acef770.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+tr-tr_windows_11_consumer_editions_version_25h2_x64_dvd_7cda446f.iso
+tr-tr_windows_11_business_editions_version_25h2_x64_dvd_9993dd20.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+th-th_windows_11_consumer_editions_version_25h2_x64_dvd_f5c3bd94.iso
+th-th_windows_11_business_editions_version_25h2_x64_dvd_8fbbddb9.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+sv-se_windows_11_consumer_editions_version_25h2_x64_dvd_ba45b3d5.iso
+sv-se_windows_11_business_editions_version_25h2_x64_dvd_c03c2823.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+sr-latn-rs_windows_11_consumer_editions_version_25h2_x64_dvd_46c43d41.iso
+sr-latn-rs_windows_11_business_editions_version_25h2_x64_dvd_24d92a87.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+sl-si
+sl-si_windows_11_business_editions_version_25h2_x64_dvd_1dfcfa9a.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+sk-sk_windows_11_consumer_editions_version_25h2_x64_dvd_42b61574.iso
+sk-sk_windows_11_business_editions_version_25h2_x64_dvd_2620fa1f.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ru-ru_windows_11_consumer_editions_version_25h2_x64_dvd_68481cc4.iso
+ru-ru_windows_11_business_editions_version_25h2_x64_dvd_d07f6151.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ro-ro_windows_11_consumer_editions_version_25h2_x64_dvd_401d868a.iso
+ro-ro_windows_11_business_editions_version_25h2_x64_dvd_b54b1104.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pt-pt_windows_11_consumer_editions_version_25h2_x64_dvd_68e233de.iso
+pt-pt_windows_11_business_editions_version_25h2_x64_dvd_e6e3088b.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pt-br_windows_11_consumer_editions_version_25h2_x64_dvd_d4d3cf4d.iso
+pt-br_windows_11_business_editions_version_25h2_x64_dvd_dd40dfe0.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+pl-pl_windows_11_consumer_editions_version_25h2_x64_dvd_4c960909.iso
+pl-pl_windows_11_business_editions_version_25h2_x64_dvd_c9337e48.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+nl-nl_windows_11_consumer_editions_version_25h2_x64_dvd_2c75fa1e.iso
+nl-nl_windows_11_business_editions_version_25h2_x64_dvd_d91e6197.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+nb-no_windows_11_consumer_editions_version_25h2_x64_dvd_d8e522da.iso
+nb-no_windows_11_business_editions_version_25h2_x64_dvd_4bca5a0b.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+lv-lv_windows_11_consumer_editions_version_25h2_x64_dvd_a003f9ab.iso
+lv-lv_windows_11_business_editions_version_25h2_x64_dvd_59e68b12.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+lt-lt_windows_11_consumer_editions_version_25h2_x64_dvd_5f9cea94.iso
+lt-lt_windows_11_business_editions_version_25h2_x64_dvd_6c6b9ff6.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ko-kr_windows_11_consumer_editions_version_25h2_x64_dvd_e8080704.iso
+ko-kr_windows_11_business_editions_version_25h2_x64_dvd_0a0060e5.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ja-jp_windows_11_consumer_editions_version_25h2_x64_dvd_cd83d3e7.iso
+ja-jp_windows_11_business_editions_version_25h2_x64_dvd_64383c62.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+it-it_windows_11_consumer_editions_version_25h2_x64_dvd_8eece3a4.iso
+it-it_windows_11_business_editions_version_25h2_x64_dvd_58b38651.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+hu-hu_windows_11_consumer_editions_version_25h2_x64_dvd_b74a194b.iso
+hu-hu_windows_11_business_editions_version_25h2_x64_dvd_ccacc050.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+hr-hr_windows_11_consumer_editions_version_25h2_x64_dvd_332acc0a.iso
+hr-hr_windows_11_business_editions_version_25h2_x64_dvd_867ed22c.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+he-il_windows_11_consumer_editions_version_25h2_x64_dvd_7ba9380d.iso
+he-il_windows_11_business_editions_version_25h2_x64_dvd_fc87bf75.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+et-ee_windows_11_consumer_editions_version_25h2_x64_dvd_6e378872.iso
+et-ee_windows_11_business_editions_version_25h2_x64_dvd_a4bfc072.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+de-de_windows_11_consumer_editions_version_25h2_x64_dvd_d619edf8.iso
+de-de_windows_11_business_editions_version_25h2_x64_dvd_50baf378.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ar-sa_windows_11_consumer_editions_version_25h2_x64_dvd_49defffb.iso
+ar-sa_windows_11_business_editions_version_25h2_x64_dvd_228d9006.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+bg-bg_windows_11_consumer_editions_version_25h2_x64_dvd_f2f5d0d8.iso
+bg-bg_windows_11_business_editions_version_25h2_x64_dvd_bfcf3e23.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+cs-cz_windows_11_consumer_editions_version_25h2_x64_dvd_8d6f5f4a.iso
+cs-cz_windows_11_business_editions_version_25h2_x64_dvd_544cec92.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+da-dk_windows_11_consumer_editions_version_25h2_x64_dvd_859c1b9c.iso
+da-dk_windows_11_business_editions_version_25h2_x64_dvd_e6a7782f.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+el-gr_windows_11_consumer_editions_version_25h2_x64_dvd_a253d8ad.iso
+el-gr_windows_11_business_editions_version_25h2_x64_dvd_e01a8ab8.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+en-gb_windows_11_consumer_editions_version_25h2_x64_dvd_f18d2cbd.iso
+en-gb_windows_11_business_editions_version_25h2_x64_dvd_54244245.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+es-es_windows_11_consumer_editions_version_25h2_x64_dvd_d632ef37.iso
+es-es_windows_11_business_editions_version_25h2_x64_dvd_b24f689e.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+es-mx_windows_11_consumer_editions_version_25h2_x64_dvd_1a661c5a.iso
+es-mx_windows_11_business_editions_version_25h2_x64_dvd_5f163487.iso
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+fi-fi_windows_11_consumer_editions_version_25h2_x64_dvd_4ce0658e.iso
+fi-fi_windows_11_business_editions_version_25h2_x64_dvd_966eca2d.iso
+</t>
+  </si>
+  <si>
+    <t>fr-ca_windows_11_consumer_editions_version_25h2_x64_dvd_ca309939.iso
+fr-ca_windows_11_business_editions_version_25h2_x64_dvd_13b04e4c.iso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+fr-fr_windows_11_consumer_editions_version_25h2_x64_dvd_529b8796.iso
+fr-fr_windows_11_business_editions_version_25h2_x64_dvd_f18ebec2.iso
+</t>
+  </si>
+  <si>
+    <t>Download the full report</t>
+  </si>
+  <si>
+    <t>Github</t>
+  </si>
+  <si>
+    <t>Download</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+en-us_windows_11_consumer_editions_version_25h2_x64_dvd_9934ee4c.iso
+en-us_windows_11_business_editions_version_25h2_x64_dvd_41c521e7.iso
+en-us_windows_11_iot_enterprise_version_25h2_x64_dvd_67098cd6.iso
+</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -344,272 +603,23 @@
 13. Windows 11 Enterprise N
 14. Windows 11 IoT Enterprise
 15. Windows 11 IoT Enterprise Subscription
-16. Windows 11 Enterprise LTSC
-17. Windows 11 Enterprise N LTSC
-18. Windows 11 IoT Enterprise LTSC
-19. Windows 11 IoT Enterprise Subscription LTSC
-</t>
-  </si>
-  <si>
-    <t>Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742</t>
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+en-US
+ar-EG
+</t>
   </si>
   <si>
     <t xml:space="preserve">
 Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
 Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-Basic-fr-fr-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-Handwriting-fr-fr-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-</t>
-  </si>
-  <si>
-    <t>Microsoft-Windows-LanguageFeatures-Basic-zh-hk-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-Speech-zh-hk-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
-Microsoft-Windows-LanguageFeatures-TextToSpeech-zh-hk-Package~31bf3856ad364e35~amd64~~10.0.26100.1742</t>
-  </si>
-  <si>
-    <t>Report: Windows 11 25H2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2025/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-zh-tw_windows_11_consumer_editions_version_25h2_x64_dvd_5c984625.iso
-zh-tw_windows_11_business_editions_version_25h2_x64_dvd_fc876202.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-zh-cn_windows_11_consumer_editions_version_25h2_x64_dvd_0549fc93.iso
-zh-cn_windows_11_business_editions_version_25h2_x64_dvd_22759158.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-uk-ua_windows_11_consumer_editions_version_25h2_x64_dvd_422284c8.iso
-uk-ua_windows_11_business_editions_version_25h2_x64_dvd_2acef770.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-tr-tr_windows_11_consumer_editions_version_25h2_x64_dvd_7cda446f.iso
-tr-tr_windows_11_business_editions_version_25h2_x64_dvd_9993dd20.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-th-th_windows_11_consumer_editions_version_25h2_x64_dvd_f5c3bd94.iso
-th-th_windows_11_business_editions_version_25h2_x64_dvd_8fbbddb9.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-sv-se_windows_11_consumer_editions_version_25h2_x64_dvd_ba45b3d5.iso
-sv-se_windows_11_business_editions_version_25h2_x64_dvd_c03c2823.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-sr-latn-rs_windows_11_consumer_editions_version_25h2_x64_dvd_46c43d41.iso
-sr-latn-rs_windows_11_business_editions_version_25h2_x64_dvd_24d92a87.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-sl-si
-sl-si_windows_11_business_editions_version_25h2_x64_dvd_1dfcfa9a.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-sk-sk_windows_11_consumer_editions_version_25h2_x64_dvd_42b61574.iso
-sk-sk_windows_11_business_editions_version_25h2_x64_dvd_2620fa1f.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-ru-ru_windows_11_consumer_editions_version_25h2_x64_dvd_68481cc4.iso
-ru-ru_windows_11_business_editions_version_25h2_x64_dvd_d07f6151.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-ro-ro_windows_11_consumer_editions_version_25h2_x64_dvd_401d868a.iso
-ro-ro_windows_11_business_editions_version_25h2_x64_dvd_b54b1104.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-pt-pt_windows_11_consumer_editions_version_25h2_x64_dvd_68e233de.iso
-pt-pt_windows_11_business_editions_version_25h2_x64_dvd_e6e3088b.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-pt-br_windows_11_consumer_editions_version_25h2_x64_dvd_d4d3cf4d.iso
-pt-br_windows_11_business_editions_version_25h2_x64_dvd_dd40dfe0.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-pl-pl_windows_11_consumer_editions_version_25h2_x64_dvd_4c960909.iso
-pl-pl_windows_11_business_editions_version_25h2_x64_dvd_c9337e48.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-nl-nl_windows_11_consumer_editions_version_25h2_x64_dvd_2c75fa1e.iso
-nl-nl_windows_11_business_editions_version_25h2_x64_dvd_d91e6197.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-nb-no_windows_11_consumer_editions_version_25h2_x64_dvd_d8e522da.iso
-nb-no_windows_11_business_editions_version_25h2_x64_dvd_4bca5a0b.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-lv-lv_windows_11_consumer_editions_version_25h2_x64_dvd_a003f9ab.iso
-lv-lv_windows_11_business_editions_version_25h2_x64_dvd_59e68b12.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-lt-lt_windows_11_consumer_editions_version_25h2_x64_dvd_5f9cea94.iso
-lt-lt_windows_11_business_editions_version_25h2_x64_dvd_6c6b9ff6.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-ko-kr_windows_11_consumer_editions_version_25h2_x64_dvd_e8080704.iso
-ko-kr_windows_11_business_editions_version_25h2_x64_dvd_0a0060e5.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-ja-jp_windows_11_consumer_editions_version_25h2_x64_dvd_cd83d3e7.iso
-ja-jp_windows_11_business_editions_version_25h2_x64_dvd_64383c62.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-it-it_windows_11_consumer_editions_version_25h2_x64_dvd_8eece3a4.iso
-it-it_windows_11_business_editions_version_25h2_x64_dvd_58b38651.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-hu-hu_windows_11_consumer_editions_version_25h2_x64_dvd_b74a194b.iso
-hu-hu_windows_11_business_editions_version_25h2_x64_dvd_ccacc050.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-hr-hr_windows_11_consumer_editions_version_25h2_x64_dvd_332acc0a.iso
-hr-hr_windows_11_business_editions_version_25h2_x64_dvd_867ed22c.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-he-il_windows_11_consumer_editions_version_25h2_x64_dvd_7ba9380d.iso
-he-il_windows_11_business_editions_version_25h2_x64_dvd_fc87bf75.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-et-ee_windows_11_consumer_editions_version_25h2_x64_dvd_6e378872.iso
-et-ee_windows_11_business_editions_version_25h2_x64_dvd_a4bfc072.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-de-de_windows_11_consumer_editions_version_25h2_x64_dvd_d619edf8.iso
-de-de_windows_11_business_editions_version_25h2_x64_dvd_50baf378.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-ar-sa_windows_11_consumer_editions_version_25h2_x64_dvd_49defffb.iso
-ar-sa_windows_11_business_editions_version_25h2_x64_dvd_228d9006.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-bg-bg_windows_11_consumer_editions_version_25h2_x64_dvd_f2f5d0d8.iso
-bg-bg_windows_11_business_editions_version_25h2_x64_dvd_bfcf3e23.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-cs-cz_windows_11_consumer_editions_version_25h2_x64_dvd_8d6f5f4a.iso
-cs-cz_windows_11_business_editions_version_25h2_x64_dvd_544cec92.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-da-dk_windows_11_consumer_editions_version_25h2_x64_dvd_859c1b9c.iso
-da-dk_windows_11_business_editions_version_25h2_x64_dvd_e6a7782f.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-el-gr_windows_11_consumer_editions_version_25h2_x64_dvd_a253d8ad.iso
-el-gr_windows_11_business_editions_version_25h2_x64_dvd_e01a8ab8.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-en-gb_windows_11_consumer_editions_version_25h2_x64_dvd_f18d2cbd.iso
-en-gb_windows_11_business_editions_version_25h2_x64_dvd_54244245.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-es-es_windows_11_consumer_editions_version_25h2_x64_dvd_d632ef37.iso
-es-es_windows_11_business_editions_version_25h2_x64_dvd_b24f689e.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-es-mx_windows_11_consumer_editions_version_25h2_x64_dvd_1a661c5a.iso
-es-mx_windows_11_business_editions_version_25h2_x64_dvd_5f163487.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-fi-fi_windows_11_consumer_editions_version_25h2_x64_dvd_4ce0658e.iso
-fi-fi_windows_11_business_editions_version_25h2_x64_dvd_966eca2d.iso
-</t>
-  </si>
-  <si>
-    <t>fr-ca_windows_11_consumer_editions_version_25h2_x64_dvd_ca309939.iso
-fr-ca_windows_11_business_editions_version_25h2_x64_dvd_13b04e4c.iso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-fr-fr_windows_11_consumer_editions_version_25h2_x64_dvd_529b8796.iso
-fr-fr_windows_11_business_editions_version_25h2_x64_dvd_f18ebec2.iso
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-en-us_windows_11_consumer_editions_version_25h2_x64_dvd_9934ee4c.iso
-en-us_windows_11_business_editions_version_25h2_x64_dvd_41c521e7.iso
-en-us_windows_11_iot_enterprise_version_25h2_x64_dvd_67098cd6.iso
-en-us_windows_11_enterprise_ltsc_2024_x64_dvd_965cfb00.iso
-en-us_windows_11_iot_enterprise_ltsc_2024_x64_dvd_f6b14814.iso
-</t>
-  </si>
-  <si>
-    <t>Download the full report</t>
-  </si>
-  <si>
-    <t>Github</t>
-  </si>
-  <si>
-    <t>Download</t>
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
+Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.26100.1742
+Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.26100.6584
+</t>
   </si>
 </sst>
 </file>
@@ -2013,24 +2023,24 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N70"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="84.69140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="50.3828125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="20.53515625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.69140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="120.69140625" style="6" customWidth="1"/>
-    <col min="9" max="11" width="16.69140625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="25.69140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="16.69140625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.69140625" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9.15234375" style="4" hidden="1"/>
+    <col min="1" max="1" width="2.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="84.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="50.3984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="20.53125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="120.6640625" style="6" customWidth="1"/>
+    <col min="9" max="11" width="16.6640625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="25.6640625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.6640625" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9.1328125" style="4" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="4"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2045,10 +2055,10 @@
       <c r="L1" s="5"/>
       <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:14" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="4"/>
       <c r="C2" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="8"/>
@@ -2060,11 +2070,11 @@
       <c r="J2" s="26"/>
       <c r="K2" s="26"/>
       <c r="L2" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2078,7 +2088,7 @@
       <c r="L3" s="5"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2091,7 +2101,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="21"/>
     </row>
-    <row r="5" spans="1:14" ht="62.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="14"/>
       <c r="C5" s="14" t="s">
         <v>7</v>
@@ -2121,23 +2131,23 @@
         <v>45</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>52</v>
       </c>
       <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="1:14" ht="396.45" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" ht="299.25" x14ac:dyDescent="0.45">
       <c r="B6" s="2"/>
       <c r="C6" s="6">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
@@ -2156,18 +2166,18 @@
         <v>1</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="10"/>
     </row>
-    <row r="7" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B7" s="2"/>
       <c r="C7" s="6">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>57</v>
@@ -2176,10 +2186,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -2191,18 +2201,18 @@
         <v>1</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B8" s="2"/>
       <c r="C8" s="6">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>55</v>
@@ -2214,7 +2224,7 @@
         <v>64</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
@@ -2226,18 +2236,18 @@
         <v>1</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B9" s="2"/>
       <c r="C9" s="6">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>55</v>
@@ -2259,18 +2269,18 @@
         <v>1</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B10" s="2"/>
       <c r="C10" s="6">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>55</v>
@@ -2282,7 +2292,7 @@
         <v>64</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
@@ -2294,18 +2304,18 @@
         <v>1</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B11" s="2"/>
       <c r="C11" s="6">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>55</v>
@@ -2327,18 +2337,18 @@
         <v>1</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B12" s="2"/>
       <c r="C12" s="6">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>54</v>
@@ -2350,7 +2360,7 @@
         <v>64</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -2362,18 +2372,18 @@
         <v>1</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B13" s="2"/>
       <c r="C13" s="6">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>60</v>
@@ -2395,18 +2405,18 @@
         <v>1</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B14" s="2"/>
       <c r="C14" s="6">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>56</v>
@@ -2428,18 +2438,18 @@
         <v>1</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B15" s="2"/>
       <c r="C15" s="6">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>62</v>
@@ -2461,18 +2471,18 @@
         <v>1</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B16" s="2"/>
       <c r="C16" s="6">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>55</v>
@@ -2494,18 +2504,18 @@
         <v>1</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B17" s="2"/>
       <c r="C17" s="6">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>55</v>
@@ -2527,18 +2537,18 @@
         <v>1</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B18" s="2"/>
       <c r="C18" s="6">
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>59</v>
@@ -2550,7 +2560,7 @@
         <v>65</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -2562,18 +2572,18 @@
         <v>1</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B19" s="2"/>
       <c r="C19" s="6">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>56</v>
@@ -2595,18 +2605,18 @@
         <v>1</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B20" s="2"/>
       <c r="C20" s="6">
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>59</v>
@@ -2618,7 +2628,7 @@
         <v>64</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I20" s="2">
         <v>1</v>
@@ -2630,18 +2640,18 @@
         <v>1</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B21" s="2"/>
       <c r="C21" s="6">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>55</v>
@@ -2663,18 +2673,18 @@
         <v>1</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B22" s="2"/>
       <c r="C22" s="6">
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>55</v>
@@ -2696,18 +2706,18 @@
         <v>1</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B23" s="2"/>
       <c r="C23" s="6">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>55</v>
@@ -2729,18 +2739,18 @@
         <v>1</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B24" s="2"/>
       <c r="C24" s="6">
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>59</v>
@@ -2762,18 +2772,18 @@
         <v>1</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B25" s="2"/>
       <c r="C25" s="6">
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>59</v>
@@ -2795,18 +2805,18 @@
         <v>1</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B26" s="2"/>
       <c r="C26" s="6">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>60</v>
@@ -2828,18 +2838,18 @@
         <v>1</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B27" s="2"/>
       <c r="C27" s="6">
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>60</v>
@@ -2861,12 +2871,12 @@
         <v>1</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="A28" s="10" t="s">
         <v>61</v>
       </c>
@@ -2875,7 +2885,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>60</v>
@@ -2897,18 +2907,18 @@
         <v>1</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B29" s="2"/>
       <c r="C29" s="6">
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>60</v>
@@ -2930,18 +2940,18 @@
         <v>1</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B30" s="2"/>
       <c r="C30" s="6">
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>60</v>
@@ -2963,18 +2973,18 @@
         <v>1</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="31" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B31" s="2"/>
       <c r="C31" s="6">
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>57</v>
@@ -2996,18 +3006,18 @@
         <v>1</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B32" s="2"/>
       <c r="C32" s="6">
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>56</v>
@@ -3029,18 +3039,18 @@
         <v>1</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="10"/>
     </row>
-    <row r="33" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B33" s="2"/>
       <c r="C33" s="6">
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>54</v>
@@ -3062,18 +3072,18 @@
         <v>1</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="10"/>
     </row>
-    <row r="34" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B34" s="2"/>
       <c r="C34" s="6">
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>57</v>
@@ -3085,7 +3095,7 @@
         <v>64</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -3097,18 +3107,18 @@
         <v>1</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="10"/>
     </row>
-    <row r="35" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B35" s="2"/>
       <c r="C35" s="6">
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>60</v>
@@ -3130,18 +3140,18 @@
         <v>1</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B36" s="2"/>
       <c r="C36" s="6">
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>60</v>
@@ -3163,18 +3173,18 @@
         <v>1</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="10"/>
     </row>
-    <row r="37" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B37" s="2"/>
       <c r="C37" s="6">
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>62</v>
@@ -3196,18 +3206,18 @@
         <v>1</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="10"/>
     </row>
-    <row r="38" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B38" s="2"/>
       <c r="C38" s="6">
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>60</v>
@@ -3229,18 +3239,18 @@
         <v>1</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="10"/>
     </row>
-    <row r="39" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B39" s="2"/>
       <c r="C39" s="6">
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>57</v>
@@ -3252,7 +3262,7 @@
         <v>64</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I39" s="2">
         <v>1</v>
@@ -3264,18 +3274,18 @@
         <v>1</v>
       </c>
       <c r="L39" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="10"/>
     </row>
-    <row r="40" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B40" s="2"/>
       <c r="C40" s="6">
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>57</v>
@@ -3297,18 +3307,18 @@
         <v>1</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="10"/>
     </row>
-    <row r="41" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B41" s="2"/>
       <c r="C41" s="6">
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>57</v>
@@ -3320,7 +3330,7 @@
         <v>64</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I41" s="2">
         <v>1</v>
@@ -3332,18 +3342,18 @@
         <v>1</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="10"/>
     </row>
-    <row r="42" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
       <c r="C42" s="6">
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>57</v>
@@ -3365,18 +3375,18 @@
         <v>1</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="10"/>
     </row>
-    <row r="43" spans="2:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B43" s="2"/>
       <c r="C43" s="6">
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>58</v>
@@ -3388,7 +3398,7 @@
         <v>66</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I43" s="2">
         <v>1</v>
@@ -3400,12 +3410,12 @@
         <v>1</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="10"/>
     </row>
-    <row r="44" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:14" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="1"/>
@@ -3417,7 +3427,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="16"/>
       <c r="C45" s="25" t="s">
         <v>2</v>
@@ -3427,7 +3437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="18"/>
       <c r="C46" s="24" t="s">
         <v>0</v>
@@ -3444,14 +3454,14 @@
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
     </row>
-    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="19"/>
       <c r="C47" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="10"/>
@@ -3461,7 +3471,7 @@
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
     </row>
-    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3473,7 +3483,7 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
     </row>
-    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="10"/>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
@@ -3481,7 +3491,7 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
     </row>
-    <row r="50" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -3494,7 +3504,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -3507,7 +3517,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -3520,7 +3530,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -3533,7 +3543,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -3546,7 +3556,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
@@ -3559,7 +3569,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -3572,7 +3582,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -3585,7 +3595,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
@@ -3598,7 +3608,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -3611,7 +3621,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
@@ -3624,7 +3634,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
@@ -3637,7 +3647,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -3650,7 +3660,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -3663,7 +3673,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -3676,7 +3686,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -3689,7 +3699,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
@@ -3702,7 +3712,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
@@ -3715,7 +3725,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -3728,7 +3738,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -3741,7 +3751,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:12" s="10" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
